--- a/data/trans_orig/P57_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154219</t>
+          <t>155794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201775</t>
+          <t>201980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152683</t>
+          <t>156309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>203894</t>
+          <t>206239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>324898</t>
+          <t>322990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>390804</t>
+          <t>393378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>550457</t>
+          <t>550252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>598013</t>
+          <t>596438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>787085</t>
+          <t>784740</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>838296</t>
+          <t>834670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1352407</t>
+          <t>1349833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1418313</t>
+          <t>1420221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>591671</t>
+          <t>594521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>677323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>520736</t>
+          <t>521342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>602110</t>
+          <t>605980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1139476</t>
+          <t>1133049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1253962</t>
+          <t>1255656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1388588</t>
+          <t>1389511</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1475163</t>
+          <t>1472313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1376647</t>
+          <t>1372777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1458021</t>
+          <t>1457415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2791630</t>
+          <t>2789936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2906116</t>
+          <t>2912543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>182101</t>
+          <t>187218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>233327</t>
+          <t>234505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162800</t>
+          <t>166382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208717</t>
+          <t>209261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>365358</t>
+          <t>363806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>430897</t>
+          <t>428381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311607</t>
+          <t>310429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>362833</t>
+          <t>357716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>337209</t>
+          <t>336665</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>383126</t>
+          <t>379544</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659963</t>
+          <t>662479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>725502</t>
+          <t>727054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>975293</t>
+          <t>968129</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1076395</t>
+          <t>1076662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>879365</t>
+          <t>878187</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>984428</t>
+          <t>984628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1872948</t>
+          <t>1883447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2025357</t>
+          <t>2025882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2287605</t>
+          <t>2287338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2388707</t>
+          <t>2395871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2531234</t>
+          <t>2531034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2636297</t>
+          <t>2637475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4854305</t>
+          <t>4853780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5006714</t>
+          <t>4996215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149308</t>
+          <t>149850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>191313</t>
+          <t>190991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>180074</t>
+          <t>180344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>219643</t>
+          <t>221368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>339947</t>
+          <t>340319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398634</t>
+          <t>396847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>316043</t>
+          <t>316365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358048</t>
+          <t>357506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>523520</t>
+          <t>521795</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>563089</t>
+          <t>562819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>851886</t>
+          <t>853673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>910573</t>
+          <t>910201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1126693</t>
+          <t>1121467</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1632476</t>
+          <t>1593610</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>617365</t>
+          <t>637725</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1002881</t>
+          <t>1008079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1878211</t>
+          <t>1889966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2528382</t>
+          <t>2537543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655869</t>
+          <t>694735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1161652</t>
+          <t>1166878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1228324</t>
+          <t>1223126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1613840</t>
+          <t>1593480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1991169</t>
+          <t>1982008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2641340</t>
+          <t>2629585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>283495</t>
+          <t>282352</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>338535</t>
+          <t>337939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>277308</t>
+          <t>276190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>321836</t>
+          <t>321336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>572059</t>
+          <t>569675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>644163</t>
+          <t>644395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307468</t>
+          <t>308064</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>362508</t>
+          <t>363651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>336634</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381162</t>
+          <t>382280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660311</t>
+          <t>660079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>732415</t>
+          <t>734799</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1593769</t>
+          <t>1593927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2136940</t>
+          <t>2153807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1122808</t>
+          <t>1149128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1494255</t>
+          <t>1503499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2876969</t>
+          <t>2858620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3522634</t>
+          <t>3576247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1304765</t>
+          <t>1287898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1847936</t>
+          <t>1847778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2138584</t>
+          <t>2129340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2510031</t>
+          <t>2483711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3551910</t>
+          <t>3498297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4197575</t>
+          <t>4215924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155794</t>
+          <t>154904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201980</t>
+          <t>201440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156309</t>
+          <t>153510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>206239</t>
+          <t>204738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322990</t>
+          <t>319762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>393378</t>
+          <t>386685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>550252</t>
+          <t>550792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>596438</t>
+          <t>597328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>784740</t>
+          <t>786241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>834670</t>
+          <t>837469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1349833</t>
+          <t>1356526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1420221</t>
+          <t>1423449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>594521</t>
+          <t>596106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>677323</t>
+          <t>683037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>521342</t>
+          <t>522648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>605980</t>
+          <t>601460</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1133049</t>
+          <t>1134446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1255656</t>
+          <t>1252575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1389511</t>
+          <t>1383797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1472313</t>
+          <t>1470728</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1372777</t>
+          <t>1377297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1457415</t>
+          <t>1456109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2789936</t>
+          <t>2793017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2912543</t>
+          <t>2911146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187218</t>
+          <t>187539</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>234505</t>
+          <t>232788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166382</t>
+          <t>163595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209261</t>
+          <t>209833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>363806</t>
+          <t>362323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>428381</t>
+          <t>429507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310429</t>
+          <t>312146</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>357716</t>
+          <t>357395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>336665</t>
+          <t>336093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>379544</t>
+          <t>382331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>662479</t>
+          <t>661353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>727054</t>
+          <t>728537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>968129</t>
+          <t>974106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1076662</t>
+          <t>1080666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>878187</t>
+          <t>875801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>984628</t>
+          <t>986897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1883447</t>
+          <t>1871145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2025882</t>
+          <t>2027365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2287338</t>
+          <t>2283334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2395871</t>
+          <t>2389894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2531034</t>
+          <t>2528765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2637475</t>
+          <t>2639861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4853780</t>
+          <t>4852297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4996215</t>
+          <t>5008517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>169501</t>
+          <t>193206</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149850</t>
+          <t>173655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190991</t>
+          <t>218672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>199238</t>
+          <t>212265</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>180344</t>
+          <t>192556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221368</t>
+          <t>230209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>368740</t>
+          <t>405471</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>340319</t>
+          <t>376468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>396847</t>
+          <t>437212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>337855</t>
+          <t>377111</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>316365</t>
+          <t>351645</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>357506</t>
+          <t>396662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>543925</t>
+          <t>597264</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>521795</t>
+          <t>579320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>562819</t>
+          <t>616973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>881780</t>
+          <t>974375</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>853673</t>
+          <t>942634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>910201</t>
+          <t>1003378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>507356</t>
+          <t>570317</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>507356</t>
+          <t>570317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>507356</t>
+          <t>570317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>743163</t>
+          <t>809529</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>743163</t>
+          <t>809529</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>743163</t>
+          <t>809529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1250520</t>
+          <t>1379846</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1250520</t>
+          <t>1379846</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1250520</t>
+          <t>1379846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1264830</t>
+          <t>1095798</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1121467</t>
+          <t>1043140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1593610</t>
+          <t>1150417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>882649</t>
+          <t>991082</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>637725</t>
+          <t>946308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1008079</t>
+          <t>1035792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2147479</t>
+          <t>2086880</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1889966</t>
+          <t>2017116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2537543</t>
+          <t>2151967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1023515</t>
+          <t>1132679</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>694735</t>
+          <t>1078060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166878</t>
+          <t>1185337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1348556</t>
+          <t>1173339</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1223126</t>
+          <t>1128629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1593480</t>
+          <t>1218113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2372072</t>
+          <t>2306018</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1982008</t>
+          <t>2240931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2629585</t>
+          <t>2375782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288345</t>
+          <t>2228477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288345</t>
+          <t>2228477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288345</t>
+          <t>2228477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2231205</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2231205</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2231205</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4519551</t>
+          <t>4392898</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4519551</t>
+          <t>4392898</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4519551</t>
+          <t>4392898</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,32 +3015,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>308808</t>
+          <t>338246</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>282352</t>
+          <t>306290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>337939</t>
+          <t>367454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>298900</t>
+          <t>327067</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>276190</t>
+          <t>300891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>321336</t>
+          <t>349758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>607709</t>
+          <t>665313</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>569675</t>
+          <t>628147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>644395</t>
+          <t>706542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -3128,32 +3128,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>337195</t>
+          <t>372674</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308064</t>
+          <t>343466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>363651</t>
+          <t>404630</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3163,32 +3163,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>359570</t>
+          <t>405687</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>337134</t>
+          <t>382996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382280</t>
+          <t>431863</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>696765</t>
+          <t>778362</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660079</t>
+          <t>737133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>734799</t>
+          <t>815528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646003</t>
+          <t>710920</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646003</t>
+          <t>710920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646003</t>
+          <t>710920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658470</t>
+          <t>732754</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658470</t>
+          <t>732754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658470</t>
+          <t>732754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304474</t>
+          <t>1443675</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304474</t>
+          <t>1443675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304474</t>
+          <t>1443675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1743139</t>
+          <t>1627250</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1593927</t>
+          <t>1560587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2153807</t>
+          <t>1694637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1380788</t>
+          <t>1530414</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1149128</t>
+          <t>1478100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1503499</t>
+          <t>1582434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3123927</t>
+          <t>3157664</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2858620</t>
+          <t>3072930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3576247</t>
+          <t>3243434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1698566</t>
+          <t>1882464</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1287898</t>
+          <t>1815077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1847778</t>
+          <t>1949127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2252051</t>
+          <t>2176290</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2129340</t>
+          <t>2124270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2483711</t>
+          <t>2228604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3950617</t>
+          <t>4058754</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3498297</t>
+          <t>3972984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4215924</t>
+          <t>4143488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3441705</t>
+          <t>3509714</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3441705</t>
+          <t>3509714</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3441705</t>
+          <t>3509714</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3632839</t>
+          <t>3706704</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3632839</t>
+          <t>3706704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3632839</t>
+          <t>3706704</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7074544</t>
+          <t>7216418</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7074544</t>
+          <t>7216418</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7074544</t>
+          <t>7216418</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
